--- a/survey_templates/041_hot_and_cold_feedback_survey--survey_templates.xlsx
+++ b/survey_templates/041_hot_and_cold_feedback_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>intro</t>
+          <t>Introduction</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hot</t>
+          <t>hot_feedback</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>hot</t>
+          <t>Hot Feedback</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>how_hot</t>
+          <t>How Hot was it?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>cold</t>
+          <t>cold_feedback</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>cold</t>
+          <t>Cold Feedback</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>how_cold</t>
+          <t>How Cold was it?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>action</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>action_desc</t>
+          <t>Action Description</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,23 +676,23 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>rating</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>Rating</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>suggestions</t>
+          <t>rating_desc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>suggestions</t>
+          <t>Rating Description</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>next_steps</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>next_steps</t>
+          <t>Comments</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>follow_up</t>
+          <t>open_comments</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>follow_up</t>
+          <t>Open Comments</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>follow_up_desc</t>
+          <t>closed_comments</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>follow_up_desc</t>
+          <t>Closed Comments</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,23 +791,23 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>rating</t>
+          <t>rating_desc_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>rating</t>
+          <t>Rating Desc 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>rating_desc</t>
+          <t>follow_up</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>rating_desc</t>
+          <t>Follow-up Comments</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>open_comments</t>
+          <t>next_steps</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>open_comments</t>
+          <t>Next Steps</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>closed_comments</t>
+          <t>open_comments_desc</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>closed_comments</t>
+          <t>Open Comments Description</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>open_comments_desc</t>
+          <t>closed_comments_desc</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>open_comments_desc</t>
+          <t>Closed Comments Description</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,177 +911,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>closed_comments_desc</t>
+          <t>rating_desc_3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>closed_comments_desc</t>
+          <t>Rating Desc 3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>follow_up_comments</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>follow_up_comments</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>follow_up_comments_desc</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>follow_up_comments_desc</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>follow_up_comments</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>follow_up_comments</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>follow_up_comments_desc</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>follow_up_comments_desc</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>follow_up_comments</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>follow_up_comments</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>follow_up_comments</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>follow_up_comments</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>follow_up_comments_desc</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>follow_up_comments_desc</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1101,9 +940,9 @@
   <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,102 +965,102 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>hot_choices</t>
+          <t>hot_feedback_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'positive',_'label':_'positive'}</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Positive', 'label': 'Positive'}</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>hot_choices</t>
+          <t>hot_feedback_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'negative',_'label':_'negative'}</t>
+          <t>negative</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Negative', 'label': 'Negative'}</t>
+          <t>Negative</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>hot_choices</t>
+          <t>hot_feedback_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'neutral',_'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Neutral', 'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>cold_choices</t>
+          <t>cold_feedback_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'positive',_'label':_'positive'}</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Positive', 'label': 'Positive'}</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>cold_choices</t>
+          <t>cold_feedback_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'negative',_'label':_'negative'}</t>
+          <t>negative</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Negative', 'label': 'Negative'}</t>
+          <t>Negative</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>cold_choices</t>
+          <t>cold_feedback_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'neutral',_'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Neutral', 'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1072,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'positive',_'label':_'positive'}</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Positive', 'label': 'Positive'}</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1089,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'negative',_'label':_'negative'}</t>
+          <t>negative</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Negative', 'label': 'Negative'}</t>
+          <t>Negative</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1106,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'neutral',_'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Neutral', 'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1123,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'excellent',_'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Excellent', 'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1140,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'good',_'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Good', 'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1157,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'fair',_'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Fair', 'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1174,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'bad',_'label':_'bad'}</t>
+          <t>bad</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Bad', 'label': 'Bad'}</t>
+          <t>Bad</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1191,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_5,_'name':_'not_rated',_'label':_'not_rated'}</t>
+          <t>not_rated</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 5, 'name': 'Not Rated', 'label': 'Not Rated'}</t>
+          <t>Not Rated</t>
         </is>
       </c>
     </row>
